--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111950243</v>
+        <v>111950173</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465473</v>
+        <v>465440</v>
       </c>
       <c r="R2" t="n">
-        <v>6875785</v>
+        <v>6875680</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111950173</v>
+        <v>111950123</v>
       </c>
       <c r="B3" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465440</v>
+        <v>465405</v>
       </c>
       <c r="R3" t="n">
-        <v>6875680</v>
+        <v>6875710</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -878,6 +868,300 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111949354</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6875050</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111950243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blombergstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465473</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6875785</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111646755</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fläcksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465663</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6875847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111646755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111950173</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111950123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111949354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111950243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111949354</v>
+        <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
+        <v>93005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,35 +1000,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465401</v>
+        <v>465427</v>
       </c>
       <c r="R5" t="n">
-        <v>6875050</v>
+        <v>6875680</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1055,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,13 +1094,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111949354</t>
+          <t>https://artportalen.se/Sighting/136044762</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111950243</v>
+        <v>111949354</v>
       </c>
       <c r="B6" t="n">
         <v>93235</v>
@@ -1124,14 +1132,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blombergstorpet, Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465473</v>
+        <v>465401</v>
       </c>
       <c r="R6" t="n">
-        <v>6875785</v>
+        <v>6875050</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1189,7 +1197,212 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/111949354</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111950243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blombergstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6875785</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/111950243</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136044806</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465439</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6875634</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136044806</t>
         </is>
       </c>
     </row>
@@ -1200,6 +1413,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93005</v>
+        <v>93006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93006</v>
+        <v>93007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93007</v>
+        <v>93008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93008</v>
+        <v>93009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136044806</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93009</v>
+        <v>93015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136044806</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136044806</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93016</v>
+        <v>93022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136044806</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93029</v>
+        <v>93030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -992,7 +992,7 @@
         <v>136044762</v>
       </c>
       <c r="B5" t="n">
-        <v>93030</v>
+        <v>93043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>136044806</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111950123</v>
+        <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93191</v>
+        <v>93391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,35 +897,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blombergstorpet, Hjd</t>
+          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465405</v>
+        <v>465553</v>
       </c>
       <c r="R4" t="n">
-        <v>6875710</v>
+        <v>6875651</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -952,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,16 +996,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111950123</t>
+          <t>https://artportalen.se/Sighting/136489980</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136044762</v>
+        <v>111950123</v>
       </c>
       <c r="B5" t="n">
-        <v>93043</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,43 +1013,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
+          <t>Blombergstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465427</v>
+        <v>465405</v>
       </c>
       <c r="R5" t="n">
-        <v>6875680</v>
+        <v>6875710</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,16 +1099,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136044762</t>
+          <t>https://artportalen.se/Sighting/111950123</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111949354</v>
+        <v>136044762</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>93043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,35 +1116,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465401</v>
+        <v>465427</v>
       </c>
       <c r="R6" t="n">
-        <v>6875050</v>
+        <v>6875680</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1166,12 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,13 +1210,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111949354</t>
+          <t>https://artportalen.se/Sighting/136044762</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111950243</v>
+        <v>111949354</v>
       </c>
       <c r="B7" t="n">
         <v>93235</v>
@@ -1235,14 +1248,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blombergstorpet, Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465473</v>
+        <v>465401</v>
       </c>
       <c r="R7" t="n">
-        <v>6875785</v>
+        <v>6875050</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1300,54 +1313,55 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111950243</t>
+          <t>https://artportalen.se/Sighting/111949354</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136044806</v>
+        <v>111950243</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
+          <t>Blombergstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465439</v>
+        <v>465473</v>
       </c>
       <c r="R8" t="n">
-        <v>6875634</v>
+        <v>6875785</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,6 +1415,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111950243</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136044806</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blombergstorpet, Blombergstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465439</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6875634</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136044806</t>
         </is>
@@ -1415,6 +1531,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17082-2022 artfynd.xlsx
+++ b/artfynd/A 17082-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136489980</v>
       </c>
       <c r="B4" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>136044762</v>
       </c>
       <c r="B6" t="n">
-        <v>93043</v>
+        <v>93044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
